--- a/docs/downloads/04/tbl_class_marovoay_bepako.xlsx
+++ b/docs/downloads/04/tbl_class_marovoay_bepako.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,14 +394,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="E2">
-        <v>1.6</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="3">
@@ -417,14 +417,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D3">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>80.3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -440,14 +440,8 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>11</v>
-      </c>
-      <c r="E4">
-        <v>18</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -509,14 +503,8 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-      <c r="E7">
-        <v>21.1</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -578,14 +566,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E10">
-        <v>21.7</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="11">
@@ -596,19 +584,13 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>2.9</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -624,14 +606,8 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12">
-        <v>75</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -642,19 +618,13 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>25</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -670,14 +640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D14">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="E14">
-        <v>18.4</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -693,14 +663,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D15">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="E15">
-        <v>81.59999999999999</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="16">
@@ -719,12 +689,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D16">
-        <v>4</v>
-      </c>
-      <c r="E16">
-        <v>1.8</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -785,14 +749,8 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>0.5</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -854,7 +812,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D22">
@@ -923,14 +881,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D25">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E25">
-        <v>12</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="26">
@@ -941,19 +899,13 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>9</v>
-      </c>
-      <c r="E26">
-        <v>3.2</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -969,14 +921,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D27">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E27">
-        <v>55.6</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="28">
@@ -992,14 +944,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D28">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E28">
-        <v>44.4</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="29">
@@ -1018,12 +970,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D29">
-        <v>39</v>
-      </c>
-      <c r="E29">
-        <v>14.1</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1064,11 +1010,28 @@
           <t>Secondaire 1er cycle</t>
         </is>
       </c>
-      <c r="D31">
-        <v>2</v>
-      </c>
-      <c r="E31">
-        <v>0.7</v>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>6-10 ans</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>35</v>
+      </c>
+      <c r="E32">
+        <v>12.6</v>
       </c>
     </row>
   </sheetData>
